--- a/excel_db/payments.xlsx
+++ b/excel_db/payments.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>id</t>
   </si>
@@ -41,6 +41,36 @@
   </si>
   <si>
     <t>created_at</t>
+  </si>
+  <si>
+    <t>transaction_ref</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>EET001</t>
+  </si>
+  <si>
+    <t>PTA</t>
+  </si>
+  <si>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>REC-2026-001</t>
+  </si>
+  <si>
+    <t>2026-06-07 00:53:56</t>
+  </si>
+  <si>
+    <t>completed</t>
   </si>
 </sst>
 </file>
@@ -398,10 +428,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -428,6 +458,44 @@
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>200</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
